--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3020" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3048" uniqueCount="501">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Device.id</t>
@@ -310,10 +310,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Device.meta.id</t>
   </si>
   <si>
@@ -487,6 +494,9 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Device.meta.tag</t>
   </si>
   <si>
@@ -603,39 +613,29 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Device.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>Device.extension:as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
+    <t>Device.extension:as-ext-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization}
 </t>
   </si>
   <si>
-    <t>AS HealthcareService Autorization Extension</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
+    <t>AS Authorization Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations des activités (HealthcareService) sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels (Device) lourds autorisés.</t>
   </si>
   <si>
     <t>Device.modifierExtension</t>
@@ -841,7 +841,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -869,6 +877,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -885,6 +897,12 @@
     <t>The reference to the definition for the device.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>Device.udiCarrier</t>
   </si>
   <si>
@@ -938,6 +956,9 @@
   </si>
   <si>
     <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -970,6 +991,9 @@
 http://hl7.org/fhir/NamingSystem/iccbba-other-di.</t>
   </si>
   <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
     <t>Role.id.root</t>
   </si>
   <si>
@@ -1095,10 +1119,16 @@
     <t>Reason for the dtatus of the Device availability.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>The availability status reason of the device.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason</t>
+  </si>
+  <si>
+    <t>CD</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1348,6 +1378,9 @@
     <t>A single component of the device version.</t>
   </si>
   <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
+  </si>
+  <si>
     <t>Device.version.value</t>
   </si>
   <si>
@@ -1397,6 +1430,16 @@
     <t>Property value as a quantity.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
@@ -1463,6 +1506,10 @@
     <t>used for troubleshooting etc.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.scopedRole[typeCode=CON].player</t>
   </si>
   <si>
@@ -1514,6 +1561,9 @@
   </si>
   <si>
     <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>.text</t>
@@ -1858,9 +1908,9 @@
   <dimension ref="A1:AM86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.01171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.92578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.6015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.67578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1893,7 +1943,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="143.74609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
@@ -2331,13 +2381,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>76</v>
@@ -2348,10 +2398,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2374,13 +2424,13 @@
         <v>76</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2431,7 +2481,7 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
@@ -2446,7 +2496,7 @@
         <v>76</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>76</v>
@@ -2457,14 +2507,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2483,16 +2533,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2530,19 +2580,19 @@
         <v>76</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -2551,13 +2601,13 @@
         <v>78</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>76</v>
@@ -2568,13 +2618,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>76</v>
@@ -2596,13 +2646,13 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2653,7 +2703,7 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
@@ -2662,10 +2712,10 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
@@ -2679,10 +2729,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2708,13 +2758,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2764,7 +2814,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2773,13 +2823,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>76</v>
@@ -2790,10 +2840,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2816,16 +2866,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2875,7 +2925,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2884,13 +2934,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2901,10 +2951,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2927,16 +2977,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2986,7 +3036,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2995,13 +3045,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -3012,10 +3062,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3038,16 +3088,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3097,7 +3147,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3106,13 +3156,13 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>76</v>
@@ -3123,10 +3173,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3149,16 +3199,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3184,13 +3234,13 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -3208,7 +3258,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3217,13 +3267,13 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>76</v>
@@ -3234,10 +3284,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3260,16 +3310,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3295,13 +3345,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -3319,7 +3369,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3328,13 +3378,13 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>76</v>
@@ -3345,10 +3395,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3371,16 +3421,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3430,7 +3480,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3439,13 +3489,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>76</v>
@@ -3456,10 +3506,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3482,16 +3532,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3517,13 +3567,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -3541,7 +3591,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3550,13 +3600,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3567,14 +3617,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3593,16 +3643,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3652,7 +3702,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3661,13 +3711,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3678,14 +3728,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3704,16 +3754,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3763,7 +3813,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3778,7 +3828,7 @@
         <v>76</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3789,14 +3839,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3815,15 +3865,17 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3860,17 +3912,19 @@
         <v>76</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3879,13 +3933,13 @@
         <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3896,13 +3950,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>76</v>
@@ -3924,13 +3978,13 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3981,7 +4035,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3990,10 +4044,10 @@
         <v>78</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>76</v>
@@ -4014,7 +4068,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4033,7 +4087,7 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>200</v>
@@ -4042,7 +4096,7 @@
         <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>202</v>
@@ -4082,16 +4136,16 @@
         <v>76</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -4103,13 +4157,13 @@
         <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>76</v>
@@ -4202,7 +4256,7 @@
         <v>76</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>204</v>
@@ -4214,10 +4268,10 @@
         <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>211</v>
@@ -4327,10 +4381,10 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>211</v>
@@ -4370,13 +4424,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4427,7 +4481,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4442,7 +4496,7 @@
         <v>76</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>76</v>
@@ -4460,7 +4514,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4479,16 +4533,16 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4526,19 +4580,19 @@
         <v>76</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4547,13 +4601,13 @@
         <v>78</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -4590,7 +4644,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>223</v>
@@ -4660,10 +4714,10 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>231</v>
@@ -4740,7 +4794,7 @@
         <v>76</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>239</v>
@@ -4773,10 +4827,10 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>231</v>
@@ -4816,7 +4870,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>244</v>
@@ -4886,10 +4940,10 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>251</v>
@@ -4929,7 +4983,7 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>254</v>
@@ -4997,10 +5051,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>259</v>
@@ -5048,7 +5102,9 @@
       <c r="M29" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -5097,7 +5153,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5106,13 +5162,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
@@ -5123,10 +5179,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5149,16 +5205,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5208,7 +5264,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5217,13 +5273,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -5234,10 +5290,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5260,15 +5316,17 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5317,7 +5375,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5326,13 +5384,13 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
@@ -5343,10 +5401,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5369,16 +5427,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5428,7 +5486,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5437,13 +5495,13 @@
         <v>78</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>212</v>
@@ -5454,10 +5512,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5480,13 +5538,13 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5537,7 +5595,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5552,7 +5610,7 @@
         <v>76</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
@@ -5563,14 +5621,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5589,16 +5647,16 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5636,19 +5694,19 @@
         <v>76</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5657,13 +5715,13 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
@@ -5674,14 +5732,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5700,16 +5758,16 @@
         <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>202</v>
@@ -5761,7 +5819,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5770,13 +5828,13 @@
         <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5787,14 +5845,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5813,15 +5871,17 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5870,7 +5930,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5879,31 +5939,31 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5922,15 +5982,17 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5979,7 +6041,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5988,27 +6050,27 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6031,17 +6093,19 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -6090,7 +6154,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6099,13 +6163,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -6116,14 +6180,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6142,16 +6206,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6201,7 +6265,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6210,31 +6274,31 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6253,16 +6317,16 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6312,7 +6376,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6321,27 +6385,27 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6364,17 +6428,19 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O41" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
@@ -6402,10 +6468,10 @@
         <v>227</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>76</v>
@@ -6423,7 +6489,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6432,13 +6498,13 @@
         <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
@@ -6449,10 +6515,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6475,16 +6541,16 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6513,10 +6579,10 @@
         <v>227</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6534,7 +6600,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6543,16 +6609,16 @@
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>76</v>
@@ -6560,10 +6626,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6589,12 +6655,14 @@
         <v>234</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>76</v>
@@ -6619,13 +6687,13 @@
         <v>76</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>76</v>
@@ -6643,7 +6711,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6652,16 +6720,16 @@
         <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>76</v>
@@ -6669,14 +6737,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6695,16 +6763,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6754,7 +6822,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6763,27 +6831,27 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6806,15 +6874,17 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6863,7 +6933,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6872,27 +6942,27 @@
         <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6915,13 +6985,13 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6972,7 +7042,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6981,27 +7051,27 @@
         <v>84</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7024,13 +7094,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7081,7 +7151,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7090,27 +7160,27 @@
         <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7133,15 +7203,17 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7190,7 +7262,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7199,27 +7271,27 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7242,16 +7314,16 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7301,7 +7373,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7310,16 +7382,16 @@
         <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>76</v>
@@ -7327,10 +7399,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7353,13 +7425,13 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7410,7 +7482,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7419,13 +7491,13 @@
         <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
@@ -7436,10 +7508,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7462,13 +7534,13 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7519,7 +7591,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7534,7 +7606,7 @@
         <v>76</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7545,14 +7617,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7571,16 +7643,16 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7618,19 +7690,19 @@
         <v>76</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7639,13 +7711,13 @@
         <v>78</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
@@ -7656,14 +7728,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7682,16 +7754,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>202</v>
@@ -7743,7 +7815,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7752,13 +7824,13 @@
         <v>78</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
@@ -7769,14 +7841,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7795,15 +7867,17 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -7852,7 +7926,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>84</v>
@@ -7861,13 +7935,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>76</v>
@@ -7878,10 +7952,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7904,15 +7978,17 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7940,10 +8016,10 @@
         <v>227</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>76</v>
@@ -7961,7 +8037,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>84</v>
@@ -7970,16 +8046,16 @@
         <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>76</v>
@@ -7987,10 +8063,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8013,15 +8089,17 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8070,7 +8148,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8079,16 +8157,16 @@
         <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>76</v>
@@ -8096,10 +8174,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8122,16 +8200,16 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8181,7 +8259,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8190,16 +8268,16 @@
         <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>76</v>
@@ -8207,10 +8285,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8236,12 +8314,14 @@
         <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8270,7 +8350,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>76</v>
@@ -8288,7 +8368,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8297,13 +8377,13 @@
         <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>76</v>
@@ -8314,10 +8394,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8340,13 +8420,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8397,7 +8477,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8406,13 +8486,13 @@
         <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
@@ -8423,10 +8503,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8449,13 +8529,13 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8506,7 +8586,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8521,7 +8601,7 @@
         <v>76</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
@@ -8532,14 +8612,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8558,16 +8638,16 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8605,19 +8685,19 @@
         <v>76</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8626,13 +8706,13 @@
         <v>78</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>76</v>
@@ -8643,14 +8723,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8669,16 +8749,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>202</v>
@@ -8730,7 +8810,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8739,13 +8819,13 @@
         <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>76</v>
@@ -8756,14 +8836,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8785,12 +8865,14 @@
         <v>234</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8839,7 +8921,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>84</v>
@@ -8848,13 +8930,13 @@
         <v>84</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>76</v>
@@ -8865,10 +8947,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8891,15 +8973,17 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8948,7 +9032,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8957,16 +9041,16 @@
         <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>76</v>
@@ -8974,10 +9058,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9000,13 +9084,13 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9057,7 +9141,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9066,13 +9150,13 @@
         <v>78</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>76</v>
@@ -9083,10 +9167,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9109,13 +9193,13 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9166,7 +9250,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9181,7 +9265,7 @@
         <v>76</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>76</v>
@@ -9192,14 +9276,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9218,16 +9302,16 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9265,19 +9349,19 @@
         <v>76</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9286,13 +9370,13 @@
         <v>78</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>76</v>
@@ -9303,14 +9387,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9329,16 +9413,16 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>202</v>
@@ -9390,7 +9474,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9399,13 +9483,13 @@
         <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>76</v>
@@ -9416,14 +9500,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9445,12 +9529,14 @@
         <v>234</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>76</v>
@@ -9499,7 +9585,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9508,13 +9594,13 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>76</v>
@@ -9525,10 +9611,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9554,10 +9640,10 @@
         <v>205</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9608,7 +9694,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9617,16 +9703,16 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>76</v>
+        <v>433</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>76</v>
@@ -9634,10 +9720,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9660,15 +9746,17 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>76</v>
@@ -9717,7 +9805,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>84</v>
@@ -9726,13 +9814,13 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>76</v>
@@ -9743,10 +9831,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9769,13 +9857,13 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9826,7 +9914,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9835,13 +9923,13 @@
         <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>76</v>
@@ -9852,10 +9940,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9878,13 +9966,13 @@
         <v>76</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9935,7 +10023,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9950,7 +10038,7 @@
         <v>76</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>76</v>
@@ -9961,14 +10049,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9987,16 +10075,16 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10034,19 +10122,19 @@
         <v>76</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10055,13 +10143,13 @@
         <v>78</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
@@ -10072,14 +10160,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10098,16 +10186,16 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>202</v>
@@ -10159,7 +10247,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10168,13 +10256,13 @@
         <v>78</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>76</v>
@@ -10185,10 +10273,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10214,12 +10302,14 @@
         <v>234</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>76</v>
@@ -10268,7 +10358,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>84</v>
@@ -10277,13 +10367,13 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>76</v>
@@ -10294,10 +10384,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10320,15 +10410,17 @@
         <v>76</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>76</v>
@@ -10377,7 +10469,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10386,13 +10478,13 @@
         <v>78</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>96</v>
+        <v>451</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>76</v>
+        <v>452</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>76</v>
@@ -10403,10 +10495,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10432,12 +10524,14 @@
         <v>234</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10486,7 +10580,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10495,13 +10589,13 @@
         <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>76</v>
+        <v>351</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>76</v>
@@ -10512,10 +10606,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10538,17 +10632,19 @@
         <v>76</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -10597,7 +10693,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -10606,16 +10702,16 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>76</v>
@@ -10623,10 +10719,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10649,15 +10745,17 @@
         <v>76</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>76</v>
@@ -10706,7 +10804,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -10715,16 +10813,16 @@
         <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>76</v>
@@ -10732,10 +10830,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10758,16 +10856,16 @@
         <v>76</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -10817,7 +10915,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -10826,16 +10924,16 @@
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>96</v>
+        <v>474</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>76</v>
@@ -10843,10 +10941,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10869,17 +10967,19 @@
         <v>76</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O82" t="s" s="2">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>76</v>
@@ -10928,7 +11028,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -10937,16 +11037,16 @@
         <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>76</v>
@@ -10954,10 +11054,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10980,16 +11080,16 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11039,7 +11139,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11048,16 +11148,16 @@
         <v>84</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>76</v>
@@ -11065,10 +11165,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11091,15 +11191,17 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>76</v>
@@ -11148,7 +11250,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11157,13 +11259,13 @@
         <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>76</v>
@@ -11174,10 +11276,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11203,12 +11305,14 @@
         <v>234</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>480</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>76</v>
@@ -11257,7 +11361,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11266,13 +11370,13 @@
         <v>78</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>76</v>
@@ -11283,10 +11387,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11309,15 +11413,17 @@
         <v>76</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>484</v>
+        <v>499</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>76</v>
@@ -11366,7 +11472,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -11375,13 +11481,13 @@
         <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>76</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
